--- a/VerveStacks_GBR_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_GBR_grids_kan10/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GBR_grids_kan10\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C07ED92A-F020-45A8-8D5D-726E7670F208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE31002D-49A1-4AD0-980B-D128C001C111}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2466" uniqueCount="633">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -861,18 +861,84 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_GBR_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_GBR_019</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 19</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_GBR_007</t>
   </si>
   <si>
@@ -897,108 +963,72 @@
     <t>connecting solar to buses in cluster 1</t>
   </si>
   <si>
+    <t>distr_solelc_spv_GBR_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_GBR_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_GBR_021</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 21</t>
   </si>
   <si>
-    <t>distr_solelc_spv_GBR_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_GBR_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_w297840585_GBR,e_w1262971878_GBR</t>
+  </si>
+  <si>
+    <t>e_w636630368_GBR,e_w1078532568_GBR,e_w109189896_GBR</t>
+  </si>
+  <si>
+    <t>e_w1078532568_GBR,e_w375626500_GBR,e_w25422135-400_GBR</t>
+  </si>
+  <si>
+    <t>e_w1078532568_GBR,e_w642490160_GBR</t>
+  </si>
+  <si>
+    <t>e_w1274396508-400_GBR,e_w375626500_GBR</t>
+  </si>
+  <si>
+    <t>e_w297840585_GBR</t>
+  </si>
+  <si>
+    <t>e_w1274396508-400_GBR,e_w536905500_GBR,e_w375626500_GBR</t>
+  </si>
+  <si>
+    <t>e_w568527671_GBR</t>
+  </si>
+  <si>
+    <t>e_w137050527_GBR,e_w297840585_GBR</t>
+  </si>
+  <si>
+    <t>e_w297840585_GBR,e_w568527671_GBR</t>
+  </si>
+  <si>
     <t>e_w137050527_GBR</t>
   </si>
   <si>
@@ -1014,45 +1044,12 @@
     <t>e_w636630368_GBR,e_w109189896_GBR,e_w23281217_GBR,e_w25422135-400_GBR,e_r10695345_GBR</t>
   </si>
   <si>
+    <t>e_w297840585_GBR,e_w642490160_GBR,e_w568527671_GBR</t>
+  </si>
+  <si>
     <t>e_w148382435_GBR,e_w297840585_GBR</t>
   </si>
   <si>
-    <t>e_w1274396508-400_GBR,e_w375626500_GBR</t>
-  </si>
-  <si>
-    <t>e_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR</t>
-  </si>
-  <si>
-    <t>e_w1274396508-400_GBR,e_w536905500_GBR,e_w375626500_GBR</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR,e_w642490160_GBR,e_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>e_w1078532568_GBR,e_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>e_w137050527_GBR,e_w297840585_GBR</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR,e_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>e_w1078532568_GBR,e_w375626500_GBR,e_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR,e_w1262971878_GBR</t>
-  </si>
-  <si>
-    <t>e_w636630368_GBR,e_w1078532568_GBR,e_w109189896_GBR</t>
-  </si>
-  <si>
-    <t>e_w1274396508-400_GBR,e_w260836695_GBR</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_GBR_014</t>
   </si>
   <si>
@@ -1083,66 +1080,90 @@
     <t>connecting wind onshore to buses in cluster 11</t>
   </si>
   <si>
+    <t>distr_wonelc_won_GBR_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_GBR_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_GBR_006</t>
   </si>
   <si>
     <t>connecting wind onshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wonelc_won_GBR_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_GBR_008</t>
   </si>
   <si>
@@ -1155,30 +1176,6 @@
     <t>connecting wind onshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wonelc_won_GBR_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_GBR_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
     <t>elc_won_GBR_014</t>
   </si>
   <si>
@@ -1200,84 +1197,81 @@
     <t>elc_won_GBR_011</t>
   </si>
   <si>
+    <t>elc_won_GBR_007</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_019</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_015</t>
+  </si>
+  <si>
+    <t>e_w137050527_GBR,e_w297840585_GBR,e_w148382435_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_005</t>
+  </si>
+  <si>
+    <t>e_w636630368_GBR,e_w23281217_GBR,e_w109189896_GBR,e_r10695345_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_009</t>
+  </si>
+  <si>
+    <t>e_w1274396508-400_GBR,e_w636630368_GBR,e_w375626500_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_021</t>
+  </si>
+  <si>
+    <t>e_w568527671_GBR,e_w642490160_GBR,e_w1078532568_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_020</t>
+  </si>
+  <si>
+    <t>e_w297840585_GBR,e_w148382435_GBR,e_w642490160_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_003</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_012</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_001</t>
+  </si>
+  <si>
+    <t>e_w375626500_GBR,e_w642490160_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_017</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_004</t>
+  </si>
+  <si>
+    <t>e_w636630368_GBR,e_w1078532568_GBR,e_w642490160_GBR,e_w375626500_GBR,e_w25422135-400_GBR</t>
+  </si>
+  <si>
+    <t>elc_won_GBR_016</t>
+  </si>
+  <si>
+    <t>e_w297840585_GBR,e_w1262971878_GBR,e_w568527671_GBR</t>
+  </si>
+  <si>
     <t>elc_won_GBR_006</t>
   </si>
   <si>
     <t>e_w636630368_GBR,e_w109189896_GBR,e_w1078532568_GBR,e_w25422135-400_GBR,e_r10695345_GBR</t>
   </si>
   <si>
-    <t>elc_won_GBR_020</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR,e_w148382435_GBR,e_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_003</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_001</t>
-  </si>
-  <si>
-    <t>e_w375626500_GBR,e_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_007</t>
-  </si>
-  <si>
-    <t>e_w260836695_GBR,e_w1274396508-400_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_019</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_012</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_017</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_004</t>
-  </si>
-  <si>
-    <t>e_w636630368_GBR,e_w1078532568_GBR,e_w642490160_GBR,e_w375626500_GBR,e_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_016</t>
-  </si>
-  <si>
-    <t>e_w297840585_GBR,e_w1262971878_GBR,e_w568527671_GBR</t>
-  </si>
-  <si>
     <t>elc_won_GBR_008</t>
   </si>
   <si>
     <t>elc_won_GBR_018</t>
   </si>
   <si>
-    <t>elc_won_GBR_015</t>
-  </si>
-  <si>
-    <t>e_w137050527_GBR,e_w297840585_GBR,e_w148382435_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_005</t>
-  </si>
-  <si>
-    <t>e_w636630368_GBR,e_w23281217_GBR,e_w109189896_GBR,e_r10695345_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_009</t>
-  </si>
-  <si>
-    <t>e_w1274396508-400_GBR,e_w636630368_GBR,e_w375626500_GBR</t>
-  </si>
-  <si>
-    <t>elc_won_GBR_021</t>
-  </si>
-  <si>
-    <t>e_w568527671_GBR,e_w642490160_GBR,e_w1078532568_GBR</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_GBR_018</t>
   </si>
   <si>
@@ -1290,6 +1284,96 @@
     <t>connecting wind offshore to buses in cluster 12</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_GBR_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_032</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_033</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_025</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_034</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_027</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_GBR_010</t>
   </si>
   <si>
@@ -1302,6 +1386,48 @@
     <t>connecting wind offshore to buses in cluster 15</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_GBR_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_031</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_029</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 29</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_GBR_005</t>
   </si>
   <si>
@@ -1326,174 +1452,123 @@
     <t>connecting wind offshore to buses in cluster 26</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_GBR_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_GBR_028</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 28</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_GBR_001</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_GBR_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_031</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_029</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_028</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_032</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_033</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_025</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_034</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_027</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_GBR_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
     <t>elc_wof_GBR_018</t>
   </si>
   <si>
     <t>elc_wof_GBR_012</t>
   </si>
   <si>
+    <t>elc_wof_GBR_008</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_007</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_032</t>
+  </si>
+  <si>
+    <t>e_w642490160_GBR,e_w568527671_GBR</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_002</t>
+  </si>
+  <si>
+    <t>e_w636630368_GBR,e_w23281217_GBR</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_033</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_006</t>
+  </si>
+  <si>
+    <t>e_w1274396508-400_GBR,e_w636630368_GBR</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_023</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_025</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_034</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_027</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_016</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_011</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_022</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_020</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_024</t>
+  </si>
+  <si>
     <t>elc_wof_GBR_010</t>
   </si>
   <si>
     <t>elc_wof_GBR_015</t>
   </si>
   <si>
+    <t>elc_wof_GBR_017</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_019</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_031</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_009</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_004</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_003</t>
+  </si>
+  <si>
+    <t>e_w636630368_GBR</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_029</t>
+  </si>
+  <si>
+    <t>e_w642490160_GBR,e_w1078532568_GBR</t>
+  </si>
+  <si>
     <t>elc_wof_GBR_005</t>
   </si>
   <si>
@@ -1512,109 +1587,25 @@
     <t>elc_wof_GBR_026</t>
   </si>
   <si>
+    <t>elc_wof_GBR_013</t>
+  </si>
+  <si>
+    <t>e_w568527671_GBR,e_w642490160_GBR</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_021</t>
+  </si>
+  <si>
+    <t>elc_wof_GBR_028</t>
+  </si>
+  <si>
+    <t>e_w1078532568_GBR,e_w25422135-400_GBR</t>
+  </si>
+  <si>
     <t>elc_wof_GBR_001</t>
   </si>
   <si>
     <t>e_r10695345_GBR,e_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_017</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_019</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_031</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_009</t>
-  </si>
-  <si>
-    <t>e_w1274396508-400_GBR,e_w636630368_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_004</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_003</t>
-  </si>
-  <si>
-    <t>e_w636630368_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_029</t>
-  </si>
-  <si>
-    <t>e_w642490160_GBR,e_w1078532568_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_013</t>
-  </si>
-  <si>
-    <t>e_w568527671_GBR,e_w642490160_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_021</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_028</t>
-  </si>
-  <si>
-    <t>e_w1078532568_GBR,e_w25422135-400_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_008</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_007</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_032</t>
-  </si>
-  <si>
-    <t>e_w642490160_GBR,e_w568527671_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_002</t>
-  </si>
-  <si>
-    <t>e_w636630368_GBR,e_w23281217_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_033</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_016</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_011</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_022</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_006</t>
-  </si>
-  <si>
-    <t>e_w1274396508-400_GBR,e_w260836695_GBR,e_w636630368_GBR</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_023</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_025</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_034</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_027</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_020</t>
-  </si>
-  <si>
-    <t>elc_wof_GBR_024</t>
   </si>
   <si>
     <t>e_won_GBR_001</t>
@@ -6769,7 +6760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F06821-F3E9-4442-B3F8-E67CB8CA0DDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7479DC94-36D8-4E86-B201-2D75671A8C54}">
   <dimension ref="B9:BD44"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7007,25 +6998,25 @@
         <v>244</v>
       </c>
       <c r="Y11" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="Z11" t="s">
         <v>290</v>
       </c>
       <c r="AA11">
-        <v>0.98918097653648285</v>
+        <v>0.99551073986131355</v>
       </c>
       <c r="AB11">
-        <v>198.34876349781462</v>
+        <v>82.303102542584213</v>
       </c>
       <c r="AD11" t="s">
         <v>243</v>
       </c>
       <c r="AE11" t="s">
+        <v>307</v>
+      </c>
+      <c r="AF11" t="s">
         <v>308</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>309</v>
       </c>
       <c r="AG11" t="s">
         <v>10</v>
@@ -7040,13 +7031,13 @@
         <v>176</v>
       </c>
       <c r="AL11" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AM11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN11" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AO11">
         <v>0.99102145505694772</v>
@@ -7058,10 +7049,10 @@
         <v>243</v>
       </c>
       <c r="AS11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="AT11" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="AU11" t="s">
         <v>10</v>
@@ -7076,13 +7067,13 @@
         <v>176</v>
       </c>
       <c r="AZ11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BA11" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="BB11" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="BC11">
         <v>0.96920091663803831</v>
@@ -7153,25 +7144,25 @@
         <v>248</v>
       </c>
       <c r="Y12" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="Z12" t="s">
         <v>291</v>
       </c>
       <c r="AA12">
-        <v>0.99905872230530834</v>
+        <v>0.99912250531124169</v>
       </c>
       <c r="AB12">
-        <v>17.256757736013821</v>
+        <v>16.087402627235775</v>
       </c>
       <c r="AD12" t="s">
         <v>243</v>
       </c>
       <c r="AE12" t="s">
+        <v>309</v>
+      </c>
+      <c r="AF12" t="s">
         <v>310</v>
-      </c>
-      <c r="AF12" t="s">
-        <v>311</v>
       </c>
       <c r="AG12" t="s">
         <v>10</v>
@@ -7186,13 +7177,13 @@
         <v>176</v>
       </c>
       <c r="AL12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AM12" t="s">
+        <v>350</v>
+      </c>
+      <c r="AN12" t="s">
         <v>351</v>
-      </c>
-      <c r="AN12" t="s">
-        <v>352</v>
       </c>
       <c r="AO12">
         <v>0.98780337799760842</v>
@@ -7204,10 +7195,10 @@
         <v>243</v>
       </c>
       <c r="AS12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="AT12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="AU12" t="s">
         <v>10</v>
@@ -7222,13 +7213,13 @@
         <v>176</v>
       </c>
       <c r="AZ12" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BA12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="BB12" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="BC12">
         <v>0.99004087150646947</v>
@@ -7299,25 +7290,25 @@
         <v>250</v>
       </c>
       <c r="Y13" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="Z13" t="s">
         <v>292</v>
       </c>
       <c r="AA13">
-        <v>0.99801872743718156</v>
+        <v>0.99892654581492313</v>
       </c>
       <c r="AB13">
-        <v>36.32333031833867</v>
+        <v>19.679993393076185</v>
       </c>
       <c r="AD13" t="s">
         <v>243</v>
       </c>
       <c r="AE13" t="s">
+        <v>311</v>
+      </c>
+      <c r="AF13" t="s">
         <v>312</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>313</v>
       </c>
       <c r="AG13" t="s">
         <v>10</v>
@@ -7332,13 +7323,13 @@
         <v>176</v>
       </c>
       <c r="AL13" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AM13" t="s">
+        <v>352</v>
+      </c>
+      <c r="AN13" t="s">
         <v>353</v>
-      </c>
-      <c r="AN13" t="s">
-        <v>354</v>
       </c>
       <c r="AO13">
         <v>0.99327661764434971</v>
@@ -7350,10 +7341,10 @@
         <v>243</v>
       </c>
       <c r="AS13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="AT13" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AU13" t="s">
         <v>10</v>
@@ -7368,19 +7359,19 @@
         <v>176</v>
       </c>
       <c r="AZ13" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="BA13" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="BB13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="BC13">
-        <v>0.98042290723232273</v>
+        <v>0.97731570613907726</v>
       </c>
       <c r="BD13">
-        <v>358.91336740741741</v>
+        <v>415.87872078358413</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -7445,25 +7436,25 @@
         <v>252</v>
       </c>
       <c r="Y14" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="Z14" t="s">
         <v>293</v>
       </c>
       <c r="AA14">
-        <v>0.99770041025535183</v>
+        <v>0.9984630278586657</v>
       </c>
       <c r="AB14">
-        <v>42.159145318550571</v>
+        <v>28.177822591129338</v>
       </c>
       <c r="AD14" t="s">
         <v>243</v>
       </c>
       <c r="AE14" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF14" t="s">
         <v>314</v>
-      </c>
-      <c r="AF14" t="s">
-        <v>315</v>
       </c>
       <c r="AG14" t="s">
         <v>10</v>
@@ -7478,13 +7469,13 @@
         <v>176</v>
       </c>
       <c r="AL14" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AM14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AN14" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AO14">
         <v>0.99893403576364492</v>
@@ -7496,10 +7487,10 @@
         <v>243</v>
       </c>
       <c r="AS14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AT14" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AU14" t="s">
         <v>10</v>
@@ -7514,19 +7505,19 @@
         <v>176</v>
       </c>
       <c r="AZ14" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="BA14" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="BB14" t="s">
-        <v>372</v>
+        <v>303</v>
       </c>
       <c r="BC14">
-        <v>0.99731674163341699</v>
+        <v>0.98426933003570904</v>
       </c>
       <c r="BD14">
-        <v>49.193070054021106</v>
+        <v>288.39561601200188</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -7591,25 +7582,25 @@
         <v>254</v>
       </c>
       <c r="Y15" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="Z15" t="s">
         <v>294</v>
       </c>
       <c r="AA15">
-        <v>0.99871196970636222</v>
+        <v>0.99763452756129467</v>
       </c>
       <c r="AB15">
-        <v>23.613888716692198</v>
+        <v>43.366994709596973</v>
       </c>
       <c r="AD15" t="s">
         <v>243</v>
       </c>
       <c r="AE15" t="s">
+        <v>315</v>
+      </c>
+      <c r="AF15" t="s">
         <v>316</v>
-      </c>
-      <c r="AF15" t="s">
-        <v>317</v>
       </c>
       <c r="AG15" t="s">
         <v>10</v>
@@ -7624,10 +7615,10 @@
         <v>176</v>
       </c>
       <c r="AL15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="AM15" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AN15" t="s">
         <v>297</v>
@@ -7642,10 +7633,10 @@
         <v>243</v>
       </c>
       <c r="AS15" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AT15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="AU15" t="s">
         <v>10</v>
@@ -7660,19 +7651,19 @@
         <v>176</v>
       </c>
       <c r="AZ15" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="BA15" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="BB15" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="BC15">
-        <v>0.99588064424311062</v>
+        <v>0.992575268180234</v>
       </c>
       <c r="BD15">
-        <v>75.521522209638391</v>
+        <v>136.12008336237702</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -7737,25 +7728,25 @@
         <v>256</v>
       </c>
       <c r="Y16" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="Z16" t="s">
         <v>295</v>
       </c>
       <c r="AA16">
-        <v>0.99774137501375304</v>
+        <v>0.98366983912436434</v>
       </c>
       <c r="AB16">
-        <v>41.408124747861258</v>
+        <v>299.38628271998641</v>
       </c>
       <c r="AD16" t="s">
         <v>243</v>
       </c>
       <c r="AE16" t="s">
+        <v>317</v>
+      </c>
+      <c r="AF16" t="s">
         <v>318</v>
-      </c>
-      <c r="AF16" t="s">
-        <v>319</v>
       </c>
       <c r="AG16" t="s">
         <v>10</v>
@@ -7770,28 +7761,28 @@
         <v>176</v>
       </c>
       <c r="AL16" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="AM16" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AN16" t="s">
-        <v>358</v>
+        <v>303</v>
       </c>
       <c r="AO16">
-        <v>0.99898539590446667</v>
+        <v>0.99773032414464768</v>
       </c>
       <c r="AP16">
-        <v>18.601075084778657</v>
+        <v>41.610724014792495</v>
       </c>
       <c r="AR16" t="s">
         <v>243</v>
       </c>
       <c r="AS16" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="AT16" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="AU16" t="s">
         <v>10</v>
@@ -7806,19 +7797,19 @@
         <v>176</v>
       </c>
       <c r="AZ16" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="BA16" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="BB16" t="s">
-        <v>298</v>
+        <v>456</v>
       </c>
       <c r="BC16">
-        <v>0.9964570686529316</v>
+        <v>0.99502822680861835</v>
       </c>
       <c r="BD16">
-        <v>64.953741362920624</v>
+        <v>91.149175175330726</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -7883,25 +7874,25 @@
         <v>258</v>
       </c>
       <c r="Y17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="Z17" t="s">
         <v>296</v>
       </c>
       <c r="AA17">
-        <v>0.99763452756129467</v>
+        <v>0.99898665727249136</v>
       </c>
       <c r="AB17">
-        <v>43.366994709596973</v>
+        <v>18.577950004324432</v>
       </c>
       <c r="AD17" t="s">
         <v>243</v>
       </c>
       <c r="AE17" t="s">
+        <v>319</v>
+      </c>
+      <c r="AF17" t="s">
         <v>320</v>
-      </c>
-      <c r="AF17" t="s">
-        <v>321</v>
       </c>
       <c r="AG17" t="s">
         <v>10</v>
@@ -7916,28 +7907,28 @@
         <v>176</v>
       </c>
       <c r="AL17" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AM17" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="AN17" t="s">
-        <v>360</v>
+        <v>299</v>
       </c>
       <c r="AO17">
-        <v>0.99805818178671835</v>
+        <v>0.99646972537983036</v>
       </c>
       <c r="AP17">
-        <v>35.600000576830709</v>
+        <v>64.721701369776625</v>
       </c>
       <c r="AR17" t="s">
         <v>243</v>
       </c>
       <c r="AS17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AT17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="AU17" t="s">
         <v>10</v>
@@ -7952,19 +7943,19 @@
         <v>176</v>
       </c>
       <c r="AZ17" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="BA17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BB17" t="s">
-        <v>459</v>
+        <v>297</v>
       </c>
       <c r="BC17">
-        <v>0.98639949743681254</v>
+        <v>0.97888630460929793</v>
       </c>
       <c r="BD17">
-        <v>249.3425469917691</v>
+        <v>387.08441549620437</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8044,10 +8035,10 @@
         <v>243</v>
       </c>
       <c r="AE18" t="s">
+        <v>321</v>
+      </c>
+      <c r="AF18" t="s">
         <v>322</v>
-      </c>
-      <c r="AF18" t="s">
-        <v>323</v>
       </c>
       <c r="AG18" t="s">
         <v>10</v>
@@ -8062,28 +8053,28 @@
         <v>176</v>
       </c>
       <c r="AL18" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AM18" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="AN18" t="s">
-        <v>296</v>
+        <v>359</v>
       </c>
       <c r="AO18">
-        <v>0.99772980990230575</v>
+        <v>0.99429617225732358</v>
       </c>
       <c r="AP18">
-        <v>41.620151791061154</v>
+        <v>104.57017528240107</v>
       </c>
       <c r="AR18" t="s">
         <v>243</v>
       </c>
       <c r="AS18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AT18" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AU18" t="s">
         <v>10</v>
@@ -8098,19 +8089,19 @@
         <v>176</v>
       </c>
       <c r="AZ18" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="BA18" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="BB18" t="s">
-        <v>297</v>
+        <v>459</v>
       </c>
       <c r="BC18">
-        <v>0.96925634503873159</v>
+        <v>0.99570169328451785</v>
       </c>
       <c r="BD18">
-        <v>563.63367428992012</v>
+        <v>78.80228978384001</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8175,25 +8166,25 @@
         <v>262</v>
       </c>
       <c r="Y19" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="Z19" t="s">
         <v>298</v>
       </c>
       <c r="AA19">
-        <v>0.98366983912436434</v>
+        <v>0.99427456799152292</v>
       </c>
       <c r="AB19">
-        <v>299.38628271998641</v>
+        <v>104.9662534887472</v>
       </c>
       <c r="AD19" t="s">
         <v>243</v>
       </c>
       <c r="AE19" t="s">
+        <v>323</v>
+      </c>
+      <c r="AF19" t="s">
         <v>324</v>
-      </c>
-      <c r="AF19" t="s">
-        <v>325</v>
       </c>
       <c r="AG19" t="s">
         <v>10</v>
@@ -8208,28 +8199,28 @@
         <v>176</v>
       </c>
       <c r="AL19" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="AM19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AN19" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AO19">
-        <v>0.9978838173682989</v>
+        <v>0.99845743456741132</v>
       </c>
       <c r="AP19">
-        <v>38.79668158118622</v>
+        <v>28.280366264125743</v>
       </c>
       <c r="AR19" t="s">
         <v>243</v>
       </c>
       <c r="AS19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AT19" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AU19" t="s">
         <v>10</v>
@@ -8244,19 +8235,19 @@
         <v>176</v>
       </c>
       <c r="AZ19" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="BA19" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="BB19" t="s">
-        <v>462</v>
+        <v>297</v>
       </c>
       <c r="BC19">
-        <v>0.99586781526523005</v>
+        <v>0.96921283174894457</v>
       </c>
       <c r="BD19">
-        <v>75.756720137449378</v>
+        <v>564.43141793601615</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -8321,25 +8312,25 @@
         <v>264</v>
       </c>
       <c r="Y20" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="Z20" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="AA20">
-        <v>0.99898665727249136</v>
+        <v>0.99194215581226264</v>
       </c>
       <c r="AB20">
-        <v>18.577950004324432</v>
+        <v>147.72714344185096</v>
       </c>
       <c r="AD20" t="s">
         <v>243</v>
       </c>
       <c r="AE20" t="s">
+        <v>325</v>
+      </c>
+      <c r="AF20" t="s">
         <v>326</v>
-      </c>
-      <c r="AF20" t="s">
-        <v>327</v>
       </c>
       <c r="AG20" t="s">
         <v>10</v>
@@ -8354,28 +8345,28 @@
         <v>176</v>
       </c>
       <c r="AL20" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="AM20" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AN20" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="AO20">
-        <v>0.99773032414464768</v>
+        <v>0.99883137892105356</v>
       </c>
       <c r="AP20">
-        <v>41.610724014792495</v>
+        <v>21.424719780683844</v>
       </c>
       <c r="AR20" t="s">
         <v>243</v>
       </c>
       <c r="AS20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="AT20" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AU20" t="s">
         <v>10</v>
@@ -8390,19 +8381,19 @@
         <v>176</v>
       </c>
       <c r="AZ20" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="BA20" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="BB20" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="BC20">
-        <v>0.94241817162668706</v>
+        <v>0.96731423589597088</v>
       </c>
       <c r="BD20">
-        <v>1055.6668535107381</v>
+        <v>599.23900857386684</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -8467,25 +8458,25 @@
         <v>266</v>
       </c>
       <c r="Y21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Z21" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="AA21">
-        <v>0.99784167066985663</v>
+        <v>0.99748996383407673</v>
       </c>
       <c r="AB21">
-        <v>39.569371052628185</v>
+        <v>46.017329708594069</v>
       </c>
       <c r="AD21" t="s">
         <v>243</v>
       </c>
       <c r="AE21" t="s">
+        <v>327</v>
+      </c>
+      <c r="AF21" t="s">
         <v>328</v>
-      </c>
-      <c r="AF21" t="s">
-        <v>329</v>
       </c>
       <c r="AG21" t="s">
         <v>10</v>
@@ -8500,28 +8491,28 @@
         <v>176</v>
       </c>
       <c r="AL21" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AM21" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="AN21" t="s">
-        <v>303</v>
+        <v>365</v>
       </c>
       <c r="AO21">
-        <v>0.99646972537983036</v>
+        <v>0.99782589578241954</v>
       </c>
       <c r="AP21">
-        <v>64.721701369776625</v>
+        <v>39.858577322307625</v>
       </c>
       <c r="AR21" t="s">
         <v>243</v>
       </c>
       <c r="AS21" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="AT21" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="AU21" t="s">
         <v>10</v>
@@ -8536,19 +8527,19 @@
         <v>176</v>
       </c>
       <c r="AZ21" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="BA21" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="BB21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BC21">
-        <v>0.97882418664902682</v>
+        <v>0.98471229610085431</v>
       </c>
       <c r="BD21">
-        <v>388.22324476784212</v>
+        <v>280.27457148433695</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -8613,25 +8604,25 @@
         <v>268</v>
       </c>
       <c r="Y22" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="Z22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AA22">
-        <v>0.9984630278586657</v>
+        <v>0.98918097653648285</v>
       </c>
       <c r="AB22">
-        <v>28.177822591129338</v>
+        <v>198.34876349781462</v>
       </c>
       <c r="AD22" t="s">
         <v>243</v>
       </c>
       <c r="AE22" t="s">
+        <v>329</v>
+      </c>
+      <c r="AF22" t="s">
         <v>330</v>
-      </c>
-      <c r="AF22" t="s">
-        <v>331</v>
       </c>
       <c r="AG22" t="s">
         <v>10</v>
@@ -8646,28 +8637,28 @@
         <v>176</v>
       </c>
       <c r="AL22" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AM22" t="s">
+        <v>366</v>
+      </c>
+      <c r="AN22" t="s">
         <v>367</v>
       </c>
-      <c r="AN22" t="s">
-        <v>298</v>
-      </c>
       <c r="AO22">
-        <v>0.98745037014666581</v>
+        <v>0.99805818178671835</v>
       </c>
       <c r="AP22">
-        <v>230.0765473111276</v>
+        <v>35.600000576830709</v>
       </c>
       <c r="AR22" t="s">
         <v>243</v>
       </c>
       <c r="AS22" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="AT22" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AU22" t="s">
         <v>10</v>
@@ -8682,19 +8673,19 @@
         <v>176</v>
       </c>
       <c r="AZ22" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="BA22" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="BB22" t="s">
         <v>297</v>
       </c>
       <c r="BC22">
-        <v>0.99096494738702623</v>
+        <v>0.97652915626122327</v>
       </c>
       <c r="BD22">
-        <v>165.64263123785253</v>
+        <v>430.2988018775734</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -8759,25 +8750,25 @@
         <v>270</v>
       </c>
       <c r="Y23" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="Z23" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AA23">
-        <v>0.99427456799152292</v>
+        <v>0.99905872230530834</v>
       </c>
       <c r="AB23">
-        <v>104.9662534887472</v>
+        <v>17.256757736013821</v>
       </c>
       <c r="AD23" t="s">
         <v>243</v>
       </c>
       <c r="AE23" t="s">
+        <v>331</v>
+      </c>
+      <c r="AF23" t="s">
         <v>332</v>
-      </c>
-      <c r="AF23" t="s">
-        <v>333</v>
       </c>
       <c r="AG23" t="s">
         <v>10</v>
@@ -8792,28 +8783,28 @@
         <v>176</v>
       </c>
       <c r="AL23" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AM23" t="s">
         <v>368</v>
       </c>
       <c r="AN23" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AO23">
-        <v>0.99727591440401897</v>
+        <v>0.99772980990230575</v>
       </c>
       <c r="AP23">
-        <v>49.941569259652468</v>
+        <v>41.620151791061154</v>
       </c>
       <c r="AR23" t="s">
         <v>243</v>
       </c>
       <c r="AS23" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="AT23" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="AU23" t="s">
         <v>10</v>
@@ -8828,19 +8819,19 @@
         <v>176</v>
       </c>
       <c r="AZ23" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="BA23" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="BB23" t="s">
-        <v>467</v>
+        <v>298</v>
       </c>
       <c r="BC23">
-        <v>0.99041009752499176</v>
+        <v>0.93778886660683014</v>
       </c>
       <c r="BD23">
-        <v>175.81487870848468</v>
+        <v>1140.5374455414481</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -8905,25 +8896,25 @@
         <v>272</v>
       </c>
       <c r="Y24" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="Z24" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="AA24">
-        <v>0.99194215581226264</v>
+        <v>0.99801872743718156</v>
       </c>
       <c r="AB24">
-        <v>147.72714344185096</v>
+        <v>36.32333031833867</v>
       </c>
       <c r="AD24" t="s">
         <v>243</v>
       </c>
       <c r="AE24" t="s">
+        <v>333</v>
+      </c>
+      <c r="AF24" t="s">
         <v>334</v>
-      </c>
-      <c r="AF24" t="s">
-        <v>335</v>
       </c>
       <c r="AG24" t="s">
         <v>10</v>
@@ -8938,28 +8929,28 @@
         <v>176</v>
       </c>
       <c r="AL24" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AM24" t="s">
         <v>369</v>
       </c>
       <c r="AN24" t="s">
-        <v>370</v>
+        <v>295</v>
       </c>
       <c r="AO24">
-        <v>0.99875924881085232</v>
+        <v>0.98745037014666581</v>
       </c>
       <c r="AP24">
-        <v>22.74710513437326</v>
+        <v>230.0765473111276</v>
       </c>
       <c r="AR24" t="s">
         <v>243</v>
       </c>
       <c r="AS24" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="AT24" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AU24" t="s">
         <v>10</v>
@@ -8974,19 +8965,19 @@
         <v>176</v>
       </c>
       <c r="AZ24" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="BA24" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="BB24" t="s">
-        <v>365</v>
+        <v>298</v>
       </c>
       <c r="BC24">
-        <v>0.99376898630456478</v>
+        <v>0.99155710419025755</v>
       </c>
       <c r="BD24">
-        <v>114.23525108297801</v>
+        <v>154.78642317861073</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9051,25 +9042,25 @@
         <v>274</v>
       </c>
       <c r="Y25" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Z25" t="s">
         <v>303</v>
       </c>
       <c r="AA25">
-        <v>0.99748996383407673</v>
+        <v>0.99770041025535183</v>
       </c>
       <c r="AB25">
-        <v>46.017329708594069</v>
+        <v>42.159145318550571</v>
       </c>
       <c r="AD25" t="s">
         <v>243</v>
       </c>
       <c r="AE25" t="s">
+        <v>335</v>
+      </c>
+      <c r="AF25" t="s">
         <v>336</v>
-      </c>
-      <c r="AF25" t="s">
-        <v>337</v>
       </c>
       <c r="AG25" t="s">
         <v>10</v>
@@ -9084,28 +9075,28 @@
         <v>176</v>
       </c>
       <c r="AL25" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AM25" t="s">
+        <v>370</v>
+      </c>
+      <c r="AN25" t="s">
         <v>371</v>
       </c>
-      <c r="AN25" t="s">
-        <v>372</v>
-      </c>
       <c r="AO25">
-        <v>0.99683412903334467</v>
+        <v>0.9978838173682989</v>
       </c>
       <c r="AP25">
-        <v>58.040967722015083</v>
+        <v>38.79668158118622</v>
       </c>
       <c r="AR25" t="s">
         <v>243</v>
       </c>
       <c r="AS25" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="AT25" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="AU25" t="s">
         <v>10</v>
@@ -9120,19 +9111,19 @@
         <v>176</v>
       </c>
       <c r="AZ25" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="BA25" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="BB25" t="s">
-        <v>470</v>
+        <v>353</v>
       </c>
       <c r="BC25">
-        <v>0.99527472814281137</v>
+        <v>0.98260708365098237</v>
       </c>
       <c r="BD25">
-        <v>86.629984048458113</v>
+        <v>318.87013306532214</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9197,25 +9188,25 @@
         <v>276</v>
       </c>
       <c r="Y26" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="Z26" t="s">
         <v>304</v>
       </c>
       <c r="AA26">
-        <v>0.99892654581492313</v>
+        <v>0.99871196970636222</v>
       </c>
       <c r="AB26">
-        <v>19.679993393076185</v>
+        <v>23.613888716692198</v>
       </c>
       <c r="AD26" t="s">
         <v>243</v>
       </c>
       <c r="AE26" t="s">
+        <v>337</v>
+      </c>
+      <c r="AF26" t="s">
         <v>338</v>
-      </c>
-      <c r="AF26" t="s">
-        <v>339</v>
       </c>
       <c r="AG26" t="s">
         <v>10</v>
@@ -9230,28 +9221,28 @@
         <v>176</v>
       </c>
       <c r="AL26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AM26" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AN26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AO26">
-        <v>0.99837805786975453</v>
+        <v>0.99727591440401897</v>
       </c>
       <c r="AP26">
-        <v>29.735605721167044</v>
+        <v>49.941569259652468</v>
       </c>
       <c r="AR26" t="s">
         <v>243</v>
       </c>
       <c r="AS26" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AT26" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AU26" t="s">
         <v>10</v>
@@ -9266,19 +9257,19 @@
         <v>176</v>
       </c>
       <c r="AZ26" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="BA26" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="BB26" t="s">
-        <v>472</v>
+        <v>295</v>
       </c>
       <c r="BC26">
-        <v>0.99559483757397482</v>
+        <v>0.97201505537091792</v>
       </c>
       <c r="BD26">
-        <v>80.761311143794899</v>
+        <v>513.05731819983896</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -9343,25 +9334,25 @@
         <v>278</v>
       </c>
       <c r="Y27" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Z27" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="AA27">
-        <v>0.99551073986131355</v>
+        <v>0.98736679836778629</v>
       </c>
       <c r="AB27">
-        <v>82.303102542584213</v>
+        <v>231.60869659058531</v>
       </c>
       <c r="AD27" t="s">
         <v>243</v>
       </c>
       <c r="AE27" t="s">
+        <v>339</v>
+      </c>
+      <c r="AF27" t="s">
         <v>340</v>
-      </c>
-      <c r="AF27" t="s">
-        <v>341</v>
       </c>
       <c r="AG27" t="s">
         <v>10</v>
@@ -9376,28 +9367,28 @@
         <v>176</v>
       </c>
       <c r="AL27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AM27" t="s">
+        <v>373</v>
+      </c>
+      <c r="AN27" t="s">
         <v>374</v>
       </c>
-      <c r="AN27" t="s">
-        <v>297</v>
-      </c>
       <c r="AO27">
-        <v>0.99900350466309695</v>
+        <v>0.99875924881085232</v>
       </c>
       <c r="AP27">
-        <v>18.26908117655681</v>
+        <v>22.74710513437326</v>
       </c>
       <c r="AR27" t="s">
         <v>243</v>
       </c>
       <c r="AS27" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="AT27" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AU27" t="s">
         <v>10</v>
@@ -9412,19 +9403,19 @@
         <v>176</v>
       </c>
       <c r="AZ27" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="BA27" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="BB27" t="s">
-        <v>474</v>
+        <v>297</v>
       </c>
       <c r="BC27">
-        <v>0.9978979227000998</v>
+        <v>0.9789057414074388</v>
       </c>
       <c r="BD27">
-        <v>38.53808383150421</v>
+        <v>386.72807419695596</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -9489,25 +9480,25 @@
         <v>280</v>
       </c>
       <c r="Y28" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="Z28" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="AA28">
-        <v>0.99912250531124169</v>
+        <v>0.9954926852371877</v>
       </c>
       <c r="AB28">
-        <v>16.087402627235775</v>
+        <v>82.634103984892022</v>
       </c>
       <c r="AD28" t="s">
         <v>243</v>
       </c>
       <c r="AE28" t="s">
+        <v>341</v>
+      </c>
+      <c r="AF28" t="s">
         <v>342</v>
-      </c>
-      <c r="AF28" t="s">
-        <v>343</v>
       </c>
       <c r="AG28" t="s">
         <v>10</v>
@@ -9522,7 +9513,7 @@
         <v>176</v>
       </c>
       <c r="AL28" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AM28" t="s">
         <v>375</v>
@@ -9531,19 +9522,19 @@
         <v>376</v>
       </c>
       <c r="AO28">
-        <v>0.99429617225732358</v>
+        <v>0.99683412903334467</v>
       </c>
       <c r="AP28">
-        <v>104.57017528240107</v>
+        <v>58.040967722015083</v>
       </c>
       <c r="AR28" t="s">
         <v>243</v>
       </c>
       <c r="AS28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AT28" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AU28" t="s">
         <v>10</v>
@@ -9558,19 +9549,19 @@
         <v>176</v>
       </c>
       <c r="AZ28" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="BA28" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="BB28" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="BC28">
-        <v>0.98397719647502369</v>
+        <v>0.98042290723232273</v>
       </c>
       <c r="BD28">
-        <v>293.75139795789926</v>
+        <v>358.91336740741741</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -9635,25 +9626,25 @@
         <v>282</v>
       </c>
       <c r="Y29" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="Z29" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="AA29">
-        <v>0.98736679836778629</v>
+        <v>0.9983765534725032</v>
       </c>
       <c r="AB29">
-        <v>231.60869659058531</v>
+        <v>29.763186337441997</v>
       </c>
       <c r="AD29" t="s">
         <v>243</v>
       </c>
       <c r="AE29" t="s">
+        <v>343</v>
+      </c>
+      <c r="AF29" t="s">
         <v>344</v>
-      </c>
-      <c r="AF29" t="s">
-        <v>345</v>
       </c>
       <c r="AG29" t="s">
         <v>10</v>
@@ -9668,7 +9659,7 @@
         <v>176</v>
       </c>
       <c r="AL29" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AM29" t="s">
         <v>377</v>
@@ -9677,19 +9668,19 @@
         <v>378</v>
       </c>
       <c r="AO29">
-        <v>0.99845743456741132</v>
+        <v>0.99898539590446667</v>
       </c>
       <c r="AP29">
-        <v>28.280366264125743</v>
+        <v>18.601075084778657</v>
       </c>
       <c r="AR29" t="s">
         <v>243</v>
       </c>
       <c r="AS29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="AT29" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="AU29" t="s">
         <v>10</v>
@@ -9704,19 +9695,19 @@
         <v>176</v>
       </c>
       <c r="AZ29" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="BA29" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="BB29" t="s">
-        <v>477</v>
+        <v>376</v>
       </c>
       <c r="BC29">
-        <v>0.99084230938934226</v>
+        <v>0.99731674163341699</v>
       </c>
       <c r="BD29">
-        <v>167.89099452872443</v>
+        <v>49.193070054021106</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -9781,25 +9772,25 @@
         <v>284</v>
       </c>
       <c r="Y30" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="Z30" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="AA30">
-        <v>0.9954926852371877</v>
+        <v>0.99784167066985663</v>
       </c>
       <c r="AB30">
-        <v>82.634103984892022</v>
+        <v>39.569371052628185</v>
       </c>
       <c r="AD30" t="s">
         <v>243</v>
       </c>
       <c r="AE30" t="s">
+        <v>345</v>
+      </c>
+      <c r="AF30" t="s">
         <v>346</v>
-      </c>
-      <c r="AF30" t="s">
-        <v>347</v>
       </c>
       <c r="AG30" t="s">
         <v>10</v>
@@ -9814,28 +9805,28 @@
         <v>176</v>
       </c>
       <c r="AL30" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AM30" t="s">
         <v>379</v>
       </c>
       <c r="AN30" t="s">
-        <v>380</v>
+        <v>303</v>
       </c>
       <c r="AO30">
-        <v>0.99883137892105356</v>
+        <v>0.99837805786975453</v>
       </c>
       <c r="AP30">
-        <v>21.424719780683844</v>
+        <v>29.735605721167044</v>
       </c>
       <c r="AR30" t="s">
         <v>243</v>
       </c>
       <c r="AS30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="AT30" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AU30" t="s">
         <v>10</v>
@@ -9850,19 +9841,19 @@
         <v>176</v>
       </c>
       <c r="AZ30" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="BA30" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="BB30" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="BC30">
-        <v>0.97731570613907726</v>
+        <v>0.94241817162668706</v>
       </c>
       <c r="BD30">
-        <v>415.87872078358413</v>
+        <v>1055.6668535107381</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -9927,25 +9918,25 @@
         <v>286</v>
       </c>
       <c r="Y31" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="Z31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AA31">
-        <v>0.9983765534725032</v>
+        <v>0.99774137501375304</v>
       </c>
       <c r="AB31">
-        <v>29.763186337441997</v>
+        <v>41.408124747861258</v>
       </c>
       <c r="AD31" t="s">
         <v>243</v>
       </c>
       <c r="AE31" t="s">
+        <v>347</v>
+      </c>
+      <c r="AF31" t="s">
         <v>348</v>
-      </c>
-      <c r="AF31" t="s">
-        <v>349</v>
       </c>
       <c r="AG31" t="s">
         <v>10</v>
@@ -9960,28 +9951,28 @@
         <v>176</v>
       </c>
       <c r="AL31" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="AM31" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AN31" t="s">
-        <v>382</v>
+        <v>297</v>
       </c>
       <c r="AO31">
-        <v>0.99782589578241954</v>
+        <v>0.99900350466309695</v>
       </c>
       <c r="AP31">
-        <v>39.858577322307625</v>
+        <v>18.26908117655681</v>
       </c>
       <c r="AR31" t="s">
         <v>243</v>
       </c>
       <c r="AS31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AT31" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AU31" t="s">
         <v>10</v>
@@ -9996,19 +9987,19 @@
         <v>176</v>
       </c>
       <c r="AZ31" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="BA31" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
       <c r="BB31" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="BC31">
-        <v>0.98426933003570904</v>
+        <v>0.97882418664902682</v>
       </c>
       <c r="BD31">
-        <v>288.39561601200188</v>
+        <v>388.22324476784212</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10016,10 +10007,10 @@
         <v>243</v>
       </c>
       <c r="AS32" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="AT32" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AU32" t="s">
         <v>10</v>
@@ -10034,19 +10025,19 @@
         <v>176</v>
       </c>
       <c r="AZ32" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="BA32" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
       <c r="BB32" t="s">
-        <v>481</v>
+        <v>297</v>
       </c>
       <c r="BC32">
-        <v>0.992575268180234</v>
+        <v>0.99096494738702623</v>
       </c>
       <c r="BD32">
-        <v>136.12008336237702</v>
+        <v>165.64263123785253</v>
       </c>
     </row>
     <row r="33" spans="44:56">
@@ -10054,10 +10045,10 @@
         <v>243</v>
       </c>
       <c r="AS33" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="AT33" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AU33" t="s">
         <v>10</v>
@@ -10072,19 +10063,19 @@
         <v>176</v>
       </c>
       <c r="AZ33" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="BA33" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="BB33" t="s">
-        <v>483</v>
+        <v>459</v>
       </c>
       <c r="BC33">
-        <v>0.99502822680861835</v>
+        <v>0.99041009752499176</v>
       </c>
       <c r="BD33">
-        <v>91.149175175330726</v>
+        <v>175.81487870848468</v>
       </c>
     </row>
     <row r="34" spans="44:56">
@@ -10092,10 +10083,10 @@
         <v>243</v>
       </c>
       <c r="AS34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AT34" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AU34" t="s">
         <v>10</v>
@@ -10110,19 +10101,19 @@
         <v>176</v>
       </c>
       <c r="AZ34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="BA34" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="BB34" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="BC34">
-        <v>0.97888630460929793</v>
+        <v>0.99376898630456478</v>
       </c>
       <c r="BD34">
-        <v>387.08441549620437</v>
+        <v>114.23525108297801</v>
       </c>
     </row>
     <row r="35" spans="44:56">
@@ -10130,10 +10121,10 @@
         <v>243</v>
       </c>
       <c r="AS35" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="AT35" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="AU35" t="s">
         <v>10</v>
@@ -10148,19 +10139,19 @@
         <v>176</v>
       </c>
       <c r="AZ35" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="BA35" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="BB35" t="s">
-        <v>302</v>
+        <v>477</v>
       </c>
       <c r="BC35">
-        <v>0.93778886660683014</v>
+        <v>0.99527472814281137</v>
       </c>
       <c r="BD35">
-        <v>1140.5374455414481</v>
+        <v>86.629984048458113</v>
       </c>
     </row>
     <row r="36" spans="44:56">
@@ -10168,10 +10159,10 @@
         <v>243</v>
       </c>
       <c r="AS36" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AT36" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AU36" t="s">
         <v>10</v>
@@ -10186,19 +10177,19 @@
         <v>176</v>
       </c>
       <c r="AZ36" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="BA36" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="BB36" t="s">
-        <v>302</v>
+        <v>479</v>
       </c>
       <c r="BC36">
-        <v>0.99155710419025755</v>
+        <v>0.99559483757397482</v>
       </c>
       <c r="BD36">
-        <v>154.78642317861073</v>
+        <v>80.761311143794899</v>
       </c>
     </row>
     <row r="37" spans="44:56">
@@ -10206,10 +10197,10 @@
         <v>243</v>
       </c>
       <c r="AS37" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="AT37" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="AU37" t="s">
         <v>10</v>
@@ -10224,19 +10215,19 @@
         <v>176</v>
       </c>
       <c r="AZ37" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="BA37" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
       <c r="BB37" t="s">
-        <v>354</v>
+        <v>481</v>
       </c>
       <c r="BC37">
-        <v>0.98260708365098237</v>
+        <v>0.99588064424311062</v>
       </c>
       <c r="BD37">
-        <v>318.87013306532214</v>
+        <v>75.521522209638391</v>
       </c>
     </row>
     <row r="38" spans="44:56">
@@ -10244,10 +10235,10 @@
         <v>243</v>
       </c>
       <c r="AS38" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="AT38" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AU38" t="s">
         <v>10</v>
@@ -10262,19 +10253,19 @@
         <v>176</v>
       </c>
       <c r="AZ38" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="BA38" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="BB38" t="s">
-        <v>489</v>
+        <v>295</v>
       </c>
       <c r="BC38">
-        <v>0.99570169328451785</v>
+        <v>0.9964570686529316</v>
       </c>
       <c r="BD38">
-        <v>78.80228978384001</v>
+        <v>64.953741362920624</v>
       </c>
     </row>
     <row r="39" spans="44:56">
@@ -10282,10 +10273,10 @@
         <v>243</v>
       </c>
       <c r="AS39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="AT39" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="AU39" t="s">
         <v>10</v>
@@ -10300,19 +10291,19 @@
         <v>176</v>
       </c>
       <c r="AZ39" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="BA39" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="BB39" t="s">
-        <v>297</v>
+        <v>484</v>
       </c>
       <c r="BC39">
-        <v>0.96921283174894457</v>
+        <v>0.98639949743681254</v>
       </c>
       <c r="BD39">
-        <v>564.43141793601615</v>
+        <v>249.3425469917691</v>
       </c>
     </row>
     <row r="40" spans="44:56">
@@ -10320,10 +10311,10 @@
         <v>243</v>
       </c>
       <c r="AS40" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="AT40" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AU40" t="s">
         <v>10</v>
@@ -10338,19 +10329,19 @@
         <v>176</v>
       </c>
       <c r="AZ40" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="BA40" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="BB40" t="s">
         <v>297</v>
       </c>
       <c r="BC40">
-        <v>0.96731423589597088</v>
+        <v>0.96925634503873159</v>
       </c>
       <c r="BD40">
-        <v>599.23900857386684</v>
+        <v>563.63367428992012</v>
       </c>
     </row>
     <row r="41" spans="44:56">
@@ -10358,10 +10349,10 @@
         <v>243</v>
       </c>
       <c r="AS41" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="AT41" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="AU41" t="s">
         <v>10</v>
@@ -10376,19 +10367,19 @@
         <v>176</v>
       </c>
       <c r="AZ41" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="BA41" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="BB41" t="s">
-        <v>297</v>
+        <v>487</v>
       </c>
       <c r="BC41">
-        <v>0.98471229610085431</v>
+        <v>0.9978979227000998</v>
       </c>
       <c r="BD41">
-        <v>280.27457148433695</v>
+        <v>38.53808383150421</v>
       </c>
     </row>
     <row r="42" spans="44:56">
@@ -10396,10 +10387,10 @@
         <v>243</v>
       </c>
       <c r="AS42" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="AT42" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AU42" t="s">
         <v>10</v>
@@ -10414,19 +10405,19 @@
         <v>176</v>
       </c>
       <c r="AZ42" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="BA42" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="BB42" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="BC42">
-        <v>0.97652915626122327</v>
+        <v>0.98397719647502369</v>
       </c>
       <c r="BD42">
-        <v>430.2988018775734</v>
+        <v>293.75139795789926</v>
       </c>
     </row>
     <row r="43" spans="44:56">
@@ -10434,10 +10425,10 @@
         <v>243</v>
       </c>
       <c r="AS43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="AT43" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="AU43" t="s">
         <v>10</v>
@@ -10452,19 +10443,19 @@
         <v>176</v>
       </c>
       <c r="AZ43" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="BA43" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="BB43" t="s">
-        <v>298</v>
+        <v>490</v>
       </c>
       <c r="BC43">
-        <v>0.97201505537091792</v>
+        <v>0.99084230938934226</v>
       </c>
       <c r="BD43">
-        <v>513.05731819983896</v>
+        <v>167.89099452872443</v>
       </c>
     </row>
     <row r="44" spans="44:56">
@@ -10472,10 +10463,10 @@
         <v>243</v>
       </c>
       <c r="AS44" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="AT44" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="AU44" t="s">
         <v>10</v>
@@ -10490,19 +10481,19 @@
         <v>176</v>
       </c>
       <c r="AZ44" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="BA44" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="BB44" t="s">
-        <v>297</v>
+        <v>492</v>
       </c>
       <c r="BC44">
-        <v>0.9789057414074388</v>
+        <v>0.99586781526523005</v>
       </c>
       <c r="BD44">
-        <v>386.72807419695596</v>
+        <v>75.756720137449378</v>
       </c>
     </row>
   </sheetData>
@@ -10511,7 +10502,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93447B6E-2BFF-421D-99AD-DDF7FE3C659E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4E54BC-2864-469B-86B0-BD046F134B7E}">
   <dimension ref="B9:Z44"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -10602,10 +10593,10 @@
         <v>172</v>
       </c>
       <c r="C11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="D11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -10620,10 +10611,10 @@
         <v>176</v>
       </c>
       <c r="J11" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="K11" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="L11">
         <v>21.399583348756885</v>
@@ -10635,10 +10626,10 @@
         <v>172</v>
       </c>
       <c r="P11" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="Q11" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="R11" t="s">
         <v>10</v>
@@ -10653,10 +10644,10 @@
         <v>176</v>
       </c>
       <c r="W11" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="X11" t="s">
-        <v>461</v>
+        <v>491</v>
       </c>
       <c r="Y11">
         <v>1.4572499999999999</v>
@@ -10670,10 +10661,10 @@
         <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D12" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -10688,10 +10679,10 @@
         <v>176</v>
       </c>
       <c r="J12" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="K12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="L12">
         <v>9.1937278269053717</v>
@@ -10703,10 +10694,10 @@
         <v>172</v>
       </c>
       <c r="P12" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="Q12" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="R12" t="s">
         <v>10</v>
@@ -10721,10 +10712,10 @@
         <v>176</v>
       </c>
       <c r="W12" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="X12" t="s">
-        <v>482</v>
+        <v>455</v>
       </c>
       <c r="Y12">
         <v>4.5019999999999998</v>
@@ -10738,10 +10729,10 @@
         <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="D13" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -10756,10 +10747,10 @@
         <v>176</v>
       </c>
       <c r="J13" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="K13" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="L13">
         <v>19.989649238118904</v>
@@ -10771,10 +10762,10 @@
         <v>172</v>
       </c>
       <c r="P13" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="Q13" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="R13" t="s">
         <v>10</v>
@@ -10789,10 +10780,10 @@
         <v>176</v>
       </c>
       <c r="W13" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="X13" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="Y13">
         <v>66.279750000000007</v>
@@ -10806,10 +10797,10 @@
         <v>172</v>
       </c>
       <c r="C14" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D14" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -10824,10 +10815,10 @@
         <v>176</v>
       </c>
       <c r="J14" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="K14" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="L14">
         <v>4.3020383245962606</v>
@@ -10839,10 +10830,10 @@
         <v>172</v>
       </c>
       <c r="P14" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="Q14" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="R14" t="s">
         <v>10</v>
@@ -10857,10 +10848,10 @@
         <v>176</v>
       </c>
       <c r="W14" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="X14" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="Y14">
         <v>52.679250000000003</v>
@@ -10874,10 +10865,10 @@
         <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D15" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -10892,10 +10883,10 @@
         <v>176</v>
       </c>
       <c r="J15" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="K15" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="L15">
         <v>1.9658239311284549</v>
@@ -10907,10 +10898,10 @@
         <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="Q15" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="R15" t="s">
         <v>10</v>
@@ -10925,10 +10916,10 @@
         <v>176</v>
       </c>
       <c r="W15" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="X15" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="Y15">
         <v>41.933500000000002</v>
@@ -10942,10 +10933,10 @@
         <v>172</v>
       </c>
       <c r="C16" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="D16" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -10960,10 +10951,10 @@
         <v>176</v>
       </c>
       <c r="J16" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="K16" t="s">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="L16">
         <v>3.1267829670644942</v>
@@ -10975,10 +10966,10 @@
         <v>172</v>
       </c>
       <c r="P16" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="Q16" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="R16" t="s">
         <v>10</v>
@@ -10993,10 +10984,10 @@
         <v>176</v>
       </c>
       <c r="W16" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="X16" t="s">
-        <v>488</v>
+        <v>458</v>
       </c>
       <c r="Y16">
         <v>62.0535</v>
@@ -11010,10 +11001,10 @@
         <v>172</v>
       </c>
       <c r="C17" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D17" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -11028,10 +11019,10 @@
         <v>176</v>
       </c>
       <c r="J17" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="K17" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="L17">
         <v>11.794650527599766</v>
@@ -11043,10 +11034,10 @@
         <v>172</v>
       </c>
       <c r="P17" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="Q17" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="R17" t="s">
         <v>10</v>
@@ -11061,10 +11052,10 @@
         <v>176</v>
       </c>
       <c r="W17" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="X17" t="s">
-        <v>479</v>
+        <v>452</v>
       </c>
       <c r="Y17">
         <v>116.48625</v>
@@ -11078,10 +11069,10 @@
         <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="D18" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -11096,10 +11087,10 @@
         <v>176</v>
       </c>
       <c r="J18" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="K18" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="L18">
         <v>5.1165796137365636</v>
@@ -11111,10 +11102,10 @@
         <v>172</v>
       </c>
       <c r="P18" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="Q18" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="R18" t="s">
         <v>10</v>
@@ -11129,10 +11120,10 @@
         <v>176</v>
       </c>
       <c r="W18" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="X18" t="s">
-        <v>478</v>
+        <v>451</v>
       </c>
       <c r="Y18">
         <v>64.545749999999998</v>
@@ -11146,10 +11137,10 @@
         <v>172</v>
       </c>
       <c r="C19" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="D19" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -11164,10 +11155,10 @@
         <v>176</v>
       </c>
       <c r="J19" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="K19" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="L19">
         <v>16.551734006758473</v>
@@ -11179,10 +11170,10 @@
         <v>172</v>
       </c>
       <c r="P19" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="Q19" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="R19" t="s">
         <v>10</v>
@@ -11197,10 +11188,10 @@
         <v>176</v>
       </c>
       <c r="W19" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="X19" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="Y19">
         <v>75.108750000000001</v>
@@ -11214,10 +11205,10 @@
         <v>172</v>
       </c>
       <c r="C20" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D20" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
@@ -11232,10 +11223,10 @@
         <v>176</v>
       </c>
       <c r="J20" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="K20" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L20">
         <v>6.4387188617631219</v>
@@ -11247,10 +11238,10 @@
         <v>172</v>
       </c>
       <c r="P20" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="Q20" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="R20" t="s">
         <v>10</v>
@@ -11265,10 +11256,10 @@
         <v>176</v>
       </c>
       <c r="W20" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="X20" t="s">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="Y20">
         <v>86.993250000000003</v>
@@ -11282,10 +11273,10 @@
         <v>172</v>
       </c>
       <c r="C21" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="D21" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
@@ -11300,10 +11291,10 @@
         <v>176</v>
       </c>
       <c r="J21" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="K21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="L21">
         <v>0.90066707673908608</v>
@@ -11315,10 +11306,10 @@
         <v>172</v>
       </c>
       <c r="P21" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="Q21" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="R21" t="s">
         <v>10</v>
@@ -11333,10 +11324,10 @@
         <v>176</v>
       </c>
       <c r="W21" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="X21" t="s">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="Y21">
         <v>46.916249999999998</v>
@@ -11350,10 +11341,10 @@
         <v>172</v>
       </c>
       <c r="C22" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D22" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
@@ -11368,10 +11359,10 @@
         <v>176</v>
       </c>
       <c r="J22" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="K22" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="L22">
         <v>3.9389030102054172</v>
@@ -11383,10 +11374,10 @@
         <v>172</v>
       </c>
       <c r="P22" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="Q22" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="R22" t="s">
         <v>10</v>
@@ -11401,10 +11392,10 @@
         <v>176</v>
       </c>
       <c r="W22" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="X22" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="Y22">
         <v>44.330249999999999</v>
@@ -11418,10 +11409,10 @@
         <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D23" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -11436,10 +11427,10 @@
         <v>176</v>
       </c>
       <c r="J23" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="K23" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="L23">
         <v>2.7493737137831373</v>
@@ -11451,10 +11442,10 @@
         <v>172</v>
       </c>
       <c r="P23" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="Q23" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="R23" t="s">
         <v>10</v>
@@ -11469,10 +11460,10 @@
         <v>176</v>
       </c>
       <c r="W23" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="X23" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="Y23">
         <v>5.8137499999999998</v>
@@ -11486,10 +11477,10 @@
         <v>172</v>
       </c>
       <c r="C24" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="D24" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
@@ -11504,10 +11495,10 @@
         <v>176</v>
       </c>
       <c r="J24" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="K24" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="L24">
         <v>31.309690061164826</v>
@@ -11519,10 +11510,10 @@
         <v>172</v>
       </c>
       <c r="P24" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="Q24" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="R24" t="s">
         <v>10</v>
@@ -11537,10 +11528,10 @@
         <v>176</v>
       </c>
       <c r="W24" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="X24" t="s">
-        <v>457</v>
+        <v>482</v>
       </c>
       <c r="Y24">
         <v>0.28649999999999998</v>
@@ -11554,10 +11545,10 @@
         <v>172</v>
       </c>
       <c r="C25" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="D25" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -11572,10 +11563,10 @@
         <v>176</v>
       </c>
       <c r="J25" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="K25" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="L25">
         <v>7.2410193343179081</v>
@@ -11587,10 +11578,10 @@
         <v>172</v>
       </c>
       <c r="P25" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="Q25" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="R25" t="s">
         <v>10</v>
@@ -11605,10 +11596,10 @@
         <v>176</v>
       </c>
       <c r="W25" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="X25" t="s">
-        <v>454</v>
+        <v>470</v>
       </c>
       <c r="Y25">
         <v>3.3562500000000002</v>
@@ -11622,10 +11613,10 @@
         <v>172</v>
       </c>
       <c r="C26" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D26" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -11640,10 +11631,10 @@
         <v>176</v>
       </c>
       <c r="J26" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="K26" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L26">
         <v>7.0119734962746385</v>
@@ -11655,10 +11646,10 @@
         <v>172</v>
       </c>
       <c r="P26" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="Q26" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="R26" t="s">
         <v>10</v>
@@ -11673,10 +11664,10 @@
         <v>176</v>
       </c>
       <c r="W26" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="X26" t="s">
-        <v>485</v>
+        <v>464</v>
       </c>
       <c r="Y26">
         <v>14.58225</v>
@@ -11690,10 +11681,10 @@
         <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="D27" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
@@ -11708,10 +11699,10 @@
         <v>176</v>
       </c>
       <c r="J27" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="K27" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="L27">
         <v>14.766366589726868</v>
@@ -11723,10 +11714,10 @@
         <v>172</v>
       </c>
       <c r="P27" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="Q27" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="R27" t="s">
         <v>10</v>
@@ -11741,10 +11732,10 @@
         <v>176</v>
       </c>
       <c r="W27" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="X27" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="Y27">
         <v>84.296999999999997</v>
@@ -11758,10 +11749,10 @@
         <v>172</v>
       </c>
       <c r="C28" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D28" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -11776,10 +11767,10 @@
         <v>176</v>
       </c>
       <c r="J28" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="K28" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="L28">
         <v>0.97891244065217997</v>
@@ -11791,10 +11782,10 @@
         <v>172</v>
       </c>
       <c r="P28" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="Q28" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="R28" t="s">
         <v>10</v>
@@ -11809,10 +11800,10 @@
         <v>176</v>
       </c>
       <c r="W28" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="X28" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Y28">
         <v>41.697000000000003</v>
@@ -11826,10 +11817,10 @@
         <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D29" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -11844,10 +11835,10 @@
         <v>176</v>
       </c>
       <c r="J29" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="K29" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="L29">
         <v>9.4365862951867765</v>
@@ -11859,10 +11850,10 @@
         <v>172</v>
       </c>
       <c r="P29" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="Q29" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="R29" t="s">
         <v>10</v>
@@ -11877,10 +11868,10 @@
         <v>176</v>
       </c>
       <c r="W29" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="X29" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="Y29">
         <v>71.0655</v>
@@ -11894,10 +11885,10 @@
         <v>172</v>
       </c>
       <c r="C30" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D30" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -11912,10 +11903,10 @@
         <v>176</v>
       </c>
       <c r="J30" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="K30" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="L30">
         <v>17.563470485556486</v>
@@ -11927,10 +11918,10 @@
         <v>172</v>
       </c>
       <c r="P30" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="Q30" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="R30" t="s">
         <v>10</v>
@@ -11945,10 +11936,10 @@
         <v>176</v>
       </c>
       <c r="W30" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="X30" t="s">
-        <v>494</v>
+        <v>467</v>
       </c>
       <c r="Y30">
         <v>39.66075</v>
@@ -11962,10 +11953,10 @@
         <v>172</v>
       </c>
       <c r="C31" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="D31" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -11980,10 +11971,10 @@
         <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="K31" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="L31">
         <v>1.7380844549911334</v>
@@ -11995,10 +11986,10 @@
         <v>172</v>
       </c>
       <c r="P31" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="Q31" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="R31" t="s">
         <v>10</v>
@@ -12013,10 +12004,10 @@
         <v>176</v>
       </c>
       <c r="W31" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="X31" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="Y31">
         <v>99.740750000000006</v>
@@ -12030,10 +12021,10 @@
         <v>172</v>
       </c>
       <c r="P32" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="Q32" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="R32" t="s">
         <v>10</v>
@@ -12048,10 +12039,10 @@
         <v>176</v>
       </c>
       <c r="W32" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="X32" t="s">
-        <v>487</v>
+        <v>466</v>
       </c>
       <c r="Y32">
         <v>84.713250000000002</v>
@@ -12065,10 +12056,10 @@
         <v>172</v>
       </c>
       <c r="P33" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="Q33" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="R33" t="s">
         <v>10</v>
@@ -12083,10 +12074,10 @@
         <v>176</v>
       </c>
       <c r="W33" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="X33" t="s">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="Y33">
         <v>9.8707499999999992</v>
@@ -12100,10 +12091,10 @@
         <v>172</v>
       </c>
       <c r="P34" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="Q34" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="R34" t="s">
         <v>10</v>
@@ -12118,10 +12109,10 @@
         <v>176</v>
       </c>
       <c r="W34" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="X34" t="s">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="Y34">
         <v>82.724249999999998</v>
@@ -12135,10 +12126,10 @@
         <v>172</v>
       </c>
       <c r="P35" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="Q35" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="R35" t="s">
         <v>10</v>
@@ -12153,10 +12144,10 @@
         <v>176</v>
       </c>
       <c r="W35" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="X35" t="s">
-        <v>491</v>
+        <v>461</v>
       </c>
       <c r="Y35">
         <v>103.515</v>
@@ -12170,10 +12161,10 @@
         <v>172</v>
       </c>
       <c r="P36" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="Q36" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="R36" t="s">
         <v>10</v>
@@ -12188,10 +12179,10 @@
         <v>176</v>
       </c>
       <c r="W36" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="X36" t="s">
-        <v>460</v>
+        <v>485</v>
       </c>
       <c r="Y36">
         <v>66.305999999999997</v>
@@ -12205,10 +12196,10 @@
         <v>172</v>
       </c>
       <c r="P37" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="Q37" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="R37" t="s">
         <v>10</v>
@@ -12223,10 +12214,10 @@
         <v>176</v>
       </c>
       <c r="W37" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="X37" t="s">
-        <v>493</v>
+        <v>463</v>
       </c>
       <c r="Y37">
         <v>107.66625000000001</v>
@@ -12240,10 +12231,10 @@
         <v>172</v>
       </c>
       <c r="P38" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="Q38" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="R38" t="s">
         <v>10</v>
@@ -12258,10 +12249,10 @@
         <v>176</v>
       </c>
       <c r="W38" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="X38" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="Y38">
         <v>43.22925</v>
@@ -12275,10 +12266,10 @@
         <v>172</v>
       </c>
       <c r="P39" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="Q39" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="R39" t="s">
         <v>10</v>
@@ -12293,10 +12284,10 @@
         <v>176</v>
       </c>
       <c r="W39" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="X39" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="Y39">
         <v>43.482999999999997</v>
@@ -12310,10 +12301,10 @@
         <v>172</v>
       </c>
       <c r="P40" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="Q40" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="R40" t="s">
         <v>10</v>
@@ -12328,10 +12319,10 @@
         <v>176</v>
       </c>
       <c r="W40" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="X40" t="s">
-        <v>458</v>
+        <v>483</v>
       </c>
       <c r="Y40">
         <v>111.13800000000001</v>
@@ -12345,10 +12336,10 @@
         <v>172</v>
       </c>
       <c r="P41" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="Q41" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="R41" t="s">
         <v>10</v>
@@ -12363,10 +12354,10 @@
         <v>176</v>
       </c>
       <c r="W41" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="X41" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="Y41">
         <v>92.353250000000003</v>
@@ -12380,10 +12371,10 @@
         <v>172</v>
       </c>
       <c r="P42" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="Q42" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="R42" t="s">
         <v>10</v>
@@ -12398,10 +12389,10 @@
         <v>176</v>
       </c>
       <c r="W42" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="X42" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
       <c r="Y42">
         <v>89.172200000000004</v>
@@ -12415,10 +12406,10 @@
         <v>172</v>
       </c>
       <c r="P43" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="Q43" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="R43" t="s">
         <v>10</v>
@@ -12433,10 +12424,10 @@
         <v>176</v>
       </c>
       <c r="W43" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="X43" t="s">
-        <v>484</v>
+        <v>457</v>
       </c>
       <c r="Y43">
         <v>31.391999999999999</v>
@@ -12450,10 +12441,10 @@
         <v>172</v>
       </c>
       <c r="P44" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="Q44" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="R44" t="s">
         <v>10</v>
@@ -12468,10 +12459,10 @@
         <v>176</v>
       </c>
       <c r="W44" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="X44" t="s">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="Y44">
         <v>112.2345</v>
@@ -12486,7 +12477,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{040E05EC-3E1C-4921-B6D6-1C0B314FE07E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF7B71F3-7D5E-48B5-AD60-30F5DFC029DD}">
   <dimension ref="B9:S128"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -12553,7 +12544,7 @@
     </row>
     <row r="11" spans="2:19">
       <c r="B11" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C11" t="s">
         <v>33</v>
@@ -12571,13 +12562,13 @@
         <v>1000</v>
       </c>
       <c r="K11" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M11" t="s">
         <v>172</v>
       </c>
       <c r="N11" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="P11" t="s">
         <v>10</v>
@@ -12589,12 +12580,12 @@
         <v>247</v>
       </c>
       <c r="S11" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="12" spans="2:19">
       <c r="B12" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
@@ -12612,13 +12603,13 @@
         <v>25</v>
       </c>
       <c r="K12" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M12" t="s">
         <v>172</v>
       </c>
       <c r="N12" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="P12" t="s">
         <v>10</v>
@@ -12630,12 +12621,12 @@
         <v>247</v>
       </c>
       <c r="S12" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="13" spans="2:19">
       <c r="B13" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C13" t="s">
         <v>33</v>
@@ -12653,13 +12644,13 @@
         <v>0.497</v>
       </c>
       <c r="K13" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="M13" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="N13" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="P13" t="s">
         <v>10</v>
@@ -12671,12 +12662,12 @@
         <v>247</v>
       </c>
       <c r="S13" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14" spans="2:19">
       <c r="B14" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C14" t="s">
         <v>33</v>
@@ -12700,7 +12691,7 @@
         <v>172</v>
       </c>
       <c r="N14" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="P14" t="s">
         <v>10</v>
@@ -12712,12 +12703,12 @@
         <v>247</v>
       </c>
       <c r="S14" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="15" spans="2:19">
       <c r="B15" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C15" t="s">
         <v>33</v>
@@ -12744,13 +12735,13 @@
         <v>30</v>
       </c>
       <c r="K15" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M15" t="s">
         <v>172</v>
       </c>
       <c r="N15" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="P15" t="s">
         <v>10</v>
@@ -12762,12 +12753,12 @@
         <v>247</v>
       </c>
       <c r="S15" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" spans="2:19">
       <c r="B16" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="C16" t="s">
         <v>33</v>
@@ -12794,13 +12785,13 @@
         <v>3</v>
       </c>
       <c r="K16" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="M16" t="s">
         <v>172</v>
       </c>
       <c r="N16" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="P16" t="s">
         <v>10</v>
@@ -12812,12 +12803,12 @@
         <v>247</v>
       </c>
       <c r="S16" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="17" spans="2:19">
       <c r="B17" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C17" t="s">
         <v>33</v>
@@ -12835,13 +12826,13 @@
         <v>500</v>
       </c>
       <c r="K17" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M17" t="s">
         <v>172</v>
       </c>
       <c r="N17" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="P17" t="s">
         <v>10</v>
@@ -12853,12 +12844,12 @@
         <v>247</v>
       </c>
       <c r="S17" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="18" spans="2:19">
       <c r="B18" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C18" t="s">
         <v>33</v>
@@ -12876,13 +12867,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M18" t="s">
         <v>172</v>
       </c>
       <c r="N18" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="P18" t="s">
         <v>10</v>
@@ -12894,12 +12885,12 @@
         <v>247</v>
       </c>
       <c r="S18" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="19" spans="2:19">
       <c r="B19" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C19" t="s">
         <v>33</v>
@@ -12917,13 +12908,13 @@
         <v>1.9279999999999999</v>
       </c>
       <c r="K19" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="M19" t="s">
         <v>172</v>
       </c>
       <c r="N19" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="P19" t="s">
         <v>10</v>
@@ -12935,12 +12926,12 @@
         <v>247</v>
       </c>
       <c r="S19" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="20" spans="2:19">
       <c r="B20" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C20" t="s">
         <v>33</v>
@@ -12964,7 +12955,7 @@
         <v>172</v>
       </c>
       <c r="N20" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="P20" t="s">
         <v>10</v>
@@ -12976,12 +12967,12 @@
         <v>247</v>
       </c>
       <c r="S20" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21" spans="2:19">
       <c r="B21" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C21" t="s">
         <v>33</v>
@@ -13008,13 +12999,13 @@
         <v>30</v>
       </c>
       <c r="K21" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M21" t="s">
         <v>172</v>
       </c>
       <c r="N21" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="P21" t="s">
         <v>10</v>
@@ -13026,12 +13017,12 @@
         <v>247</v>
       </c>
       <c r="S21" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="22" spans="2:19">
       <c r="B22" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="C22" t="s">
         <v>33</v>
@@ -13058,13 +13049,13 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="M22" t="s">
         <v>172</v>
       </c>
       <c r="N22" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="P22" t="s">
         <v>10</v>
@@ -13076,18 +13067,18 @@
         <v>247</v>
       </c>
       <c r="S22" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="23" spans="2:19">
       <c r="B23" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C23" t="s">
         <v>33</v>
       </c>
       <c r="D23" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E23">
         <v>1300</v>
@@ -13099,13 +13090,13 @@
         <v>1300</v>
       </c>
       <c r="K23" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="M23" t="s">
         <v>172</v>
       </c>
       <c r="N23" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="P23" t="s">
         <v>10</v>
@@ -13117,18 +13108,18 @@
         <v>247</v>
       </c>
       <c r="S23" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="24" spans="2:19">
       <c r="B24" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C24" t="s">
         <v>33</v>
       </c>
       <c r="D24" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E24">
         <v>40</v>
@@ -13140,13 +13131,13 @@
         <v>40</v>
       </c>
       <c r="K24" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="M24" t="s">
         <v>172</v>
       </c>
       <c r="N24" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="P24" t="s">
         <v>10</v>
@@ -13158,18 +13149,18 @@
         <v>247</v>
       </c>
       <c r="S24" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="25" spans="2:19">
       <c r="B25" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C25" t="s">
         <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E25">
         <v>0.69399999999999995</v>
@@ -13181,13 +13172,13 @@
         <v>0.69399999999999995</v>
       </c>
       <c r="K25" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="M25" t="s">
         <v>172</v>
       </c>
       <c r="N25" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="P25" t="s">
         <v>10</v>
@@ -13199,18 +13190,18 @@
         <v>247</v>
       </c>
       <c r="S25" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="26" spans="2:19">
       <c r="B26" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C26" t="s">
         <v>33</v>
       </c>
       <c r="D26" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E26">
         <v>0.53300000000000003</v>
@@ -13228,7 +13219,7 @@
         <v>172</v>
       </c>
       <c r="N26" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="P26" t="s">
         <v>10</v>
@@ -13240,18 +13231,18 @@
         <v>247</v>
       </c>
       <c r="S26" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="27" spans="2:19">
       <c r="B27" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C27" t="s">
         <v>33</v>
       </c>
       <c r="D27" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -13272,13 +13263,13 @@
         <v>25</v>
       </c>
       <c r="K27" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="M27" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="N27" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="P27" t="s">
         <v>10</v>
@@ -13290,18 +13281,18 @@
         <v>247</v>
       </c>
       <c r="S27" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="28" spans="2:19">
       <c r="B28" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C28" t="s">
         <v>33</v>
       </c>
       <c r="D28" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E28">
         <v>3</v>
@@ -13322,13 +13313,13 @@
         <v>3</v>
       </c>
       <c r="K28" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="M28" t="s">
         <v>172</v>
       </c>
       <c r="N28" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="P28" t="s">
         <v>10</v>
@@ -13340,18 +13331,18 @@
         <v>247</v>
       </c>
       <c r="S28" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="29" spans="2:19">
       <c r="B29" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="C29" t="s">
         <v>33</v>
       </c>
       <c r="D29" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E29">
         <v>0.8</v>
@@ -13372,13 +13363,13 @@
         <v>0.8</v>
       </c>
       <c r="K29" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="M29" t="s">
         <v>172</v>
       </c>
       <c r="N29" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="P29" t="s">
         <v>10</v>
@@ -13390,12 +13381,12 @@
         <v>247</v>
       </c>
       <c r="S29" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="30" spans="2:19">
       <c r="B30" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C30" t="s">
         <v>33</v>
@@ -13413,12 +13404,12 @@
         <v>2500</v>
       </c>
       <c r="K30" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="31" spans="2:19">
       <c r="B31" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C31" t="s">
         <v>33</v>
@@ -13436,12 +13427,12 @@
         <v>50</v>
       </c>
       <c r="K31" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="32" spans="2:19">
       <c r="B32" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C32" t="s">
         <v>33</v>
@@ -13459,12 +13450,12 @@
         <v>0.83299999999999996</v>
       </c>
       <c r="K32" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="33" spans="2:11">
       <c r="B33" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C33" t="s">
         <v>33</v>
@@ -13487,7 +13478,7 @@
     </row>
     <row r="34" spans="2:11">
       <c r="B34" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C34" t="s">
         <v>33</v>
@@ -13514,12 +13505,12 @@
         <v>20</v>
       </c>
       <c r="K34" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="35" spans="2:11">
       <c r="B35" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="C35" t="s">
         <v>33</v>
@@ -13546,18 +13537,18 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="36" spans="2:11">
       <c r="B36" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C36" t="s">
         <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E36">
         <v>3100</v>
@@ -13569,18 +13560,18 @@
         <v>2500</v>
       </c>
       <c r="K36" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="37" spans="2:11">
       <c r="B37" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C37" t="s">
         <v>33</v>
       </c>
       <c r="D37" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E37">
         <v>80</v>
@@ -13592,18 +13583,18 @@
         <v>60</v>
       </c>
       <c r="K37" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="38" spans="2:11">
       <c r="B38" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C38" t="s">
         <v>33</v>
       </c>
       <c r="D38" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E38">
         <v>1.35</v>
@@ -13615,18 +13606,18 @@
         <v>0.98899999999999999</v>
       </c>
       <c r="K38" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="39" spans="2:11">
       <c r="B39" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C39" t="s">
         <v>33</v>
       </c>
       <c r="D39" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E39">
         <v>0.51</v>
@@ -13643,13 +13634,13 @@
     </row>
     <row r="40" spans="2:11">
       <c r="B40" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C40" t="s">
         <v>33</v>
       </c>
       <c r="D40" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E40">
         <v>30</v>
@@ -13670,18 +13661,18 @@
         <v>30</v>
       </c>
       <c r="K40" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="41" spans="2:11">
       <c r="B41" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C41" t="s">
         <v>33</v>
       </c>
       <c r="D41" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E41">
         <v>4</v>
@@ -13702,12 +13693,12 @@
         <v>4</v>
       </c>
       <c r="K41" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="42" spans="2:11">
       <c r="B42" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C42" t="s">
         <v>32</v>
@@ -13725,12 +13716,12 @@
         <v>1700</v>
       </c>
       <c r="K42" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="43" spans="2:11">
       <c r="B43" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C43" t="s">
         <v>32</v>
@@ -13748,12 +13739,12 @@
         <v>45</v>
       </c>
       <c r="K43" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="44" spans="2:11">
       <c r="B44" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C44" t="s">
         <v>32</v>
@@ -13771,12 +13762,12 @@
         <v>2.3610000000000002</v>
       </c>
       <c r="K44" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="45" spans="2:11">
       <c r="B45" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C45" t="s">
         <v>32</v>
@@ -13799,7 +13790,7 @@
     </row>
     <row r="46" spans="2:11">
       <c r="B46" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C46" t="s">
         <v>32</v>
@@ -13826,12 +13817,12 @@
         <v>40</v>
       </c>
       <c r="K46" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="47" spans="2:11">
       <c r="B47" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="C47" t="s">
         <v>32</v>
@@ -13858,12 +13849,12 @@
         <v>4</v>
       </c>
       <c r="K47" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="48" spans="2:11">
       <c r="B48" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C48" t="s">
         <v>32</v>
@@ -13881,12 +13872,12 @@
         <v>2000</v>
       </c>
       <c r="K48" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="49" spans="2:11">
       <c r="B49" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C49" t="s">
         <v>32</v>
@@ -13904,12 +13895,12 @@
         <v>60</v>
       </c>
       <c r="K49" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="50" spans="2:11">
       <c r="B50" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C50" t="s">
         <v>32</v>
@@ -13927,12 +13918,12 @@
         <v>2.3170000000000002</v>
       </c>
       <c r="K50" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="51" spans="2:11">
       <c r="B51" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C51" t="s">
         <v>32</v>
@@ -13955,7 +13946,7 @@
     </row>
     <row r="52" spans="2:11">
       <c r="B52" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C52" t="s">
         <v>32</v>
@@ -13982,12 +13973,12 @@
         <v>40</v>
       </c>
       <c r="K52" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="53" spans="2:11">
       <c r="B53" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="C53" t="s">
         <v>32</v>
@@ -14014,12 +14005,12 @@
         <v>4</v>
       </c>
       <c r="K53" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="54" spans="2:11">
       <c r="B54" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C54" t="s">
         <v>32</v>
@@ -14037,12 +14028,12 @@
         <v>2200</v>
       </c>
       <c r="K54" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="55" spans="2:11">
       <c r="B55" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C55" t="s">
         <v>32</v>
@@ -14060,12 +14051,12 @@
         <v>65</v>
       </c>
       <c r="K55" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="56" spans="2:11">
       <c r="B56" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C56" t="s">
         <v>32</v>
@@ -14083,12 +14074,12 @@
         <v>2.6389999999999998</v>
       </c>
       <c r="K56" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="57" spans="2:11">
       <c r="B57" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C57" t="s">
         <v>32</v>
@@ -14111,7 +14102,7 @@
     </row>
     <row r="58" spans="2:11">
       <c r="B58" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
@@ -14138,12 +14129,12 @@
         <v>40</v>
       </c>
       <c r="K58" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="59" spans="2:11">
       <c r="B59" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="C59" t="s">
         <v>32</v>
@@ -14170,12 +14161,12 @@
         <v>4</v>
       </c>
       <c r="K59" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="60" spans="2:11">
       <c r="B60" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C60" t="s">
         <v>32</v>
@@ -14193,12 +14184,12 @@
         <v>2300</v>
       </c>
       <c r="K60" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="61" spans="2:11">
       <c r="B61" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C61" t="s">
         <v>32</v>
@@ -14216,12 +14207,12 @@
         <v>80</v>
       </c>
       <c r="K61" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="62" spans="2:11">
       <c r="B62" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C62" t="s">
         <v>32</v>
@@ -14244,7 +14235,7 @@
     </row>
     <row r="63" spans="2:11">
       <c r="B63" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C63" t="s">
         <v>32</v>
@@ -14271,12 +14262,12 @@
         <v>40</v>
       </c>
       <c r="K63" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="64" spans="2:11">
       <c r="B64" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C64" t="s">
         <v>32</v>
@@ -14303,18 +14294,18 @@
         <v>4</v>
       </c>
       <c r="K64" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="65" spans="2:11">
       <c r="B65" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C65" t="s">
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E65">
         <v>5500</v>
@@ -14326,18 +14317,18 @@
         <v>4500</v>
       </c>
       <c r="K65" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="66" spans="2:11">
       <c r="B66" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C66" t="s">
         <v>32</v>
       </c>
       <c r="D66" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E66">
         <v>165</v>
@@ -14349,18 +14340,18 @@
         <v>135</v>
       </c>
       <c r="K66" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="67" spans="2:11">
       <c r="B67" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C67" t="s">
         <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E67">
         <v>4.4779999999999998</v>
@@ -14372,18 +14363,18 @@
         <v>3.7309999999999999</v>
       </c>
       <c r="K67" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="68" spans="2:11">
       <c r="B68" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C68" t="s">
         <v>32</v>
       </c>
       <c r="D68" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E68">
         <v>0.36</v>
@@ -14400,13 +14391,13 @@
     </row>
     <row r="69" spans="2:11">
       <c r="B69" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C69" t="s">
         <v>32</v>
       </c>
       <c r="D69" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E69">
         <v>40</v>
@@ -14427,18 +14418,18 @@
         <v>40</v>
       </c>
       <c r="K69" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="70" spans="2:11">
       <c r="B70" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="C70" t="s">
         <v>32</v>
       </c>
       <c r="D70" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E70">
         <v>5</v>
@@ -14459,18 +14450,18 @@
         <v>5</v>
       </c>
       <c r="K70" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="71" spans="2:11">
       <c r="B71" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C71" t="s">
         <v>32</v>
       </c>
       <c r="D71" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E71">
         <v>5850</v>
@@ -14482,18 +14473,18 @@
         <v>5150</v>
       </c>
       <c r="K71" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="72" spans="2:11">
       <c r="B72" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C72" t="s">
         <v>32</v>
       </c>
       <c r="D72" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E72">
         <v>205</v>
@@ -14505,18 +14496,18 @@
         <v>180</v>
       </c>
       <c r="K72" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="73" spans="2:11">
       <c r="B73" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C73" t="s">
         <v>32</v>
       </c>
       <c r="D73" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E73">
         <v>4.5830000000000002</v>
@@ -14528,18 +14519,18 @@
         <v>4.5830000000000002</v>
       </c>
       <c r="K73" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="74" spans="2:11">
       <c r="B74" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C74" t="s">
         <v>32</v>
       </c>
       <c r="D74" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E74">
         <v>0.35</v>
@@ -14556,13 +14547,13 @@
     </row>
     <row r="75" spans="2:11">
       <c r="B75" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C75" t="s">
         <v>32</v>
       </c>
       <c r="D75" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E75">
         <v>40</v>
@@ -14583,18 +14574,18 @@
         <v>40</v>
       </c>
       <c r="K75" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="76" spans="2:11">
       <c r="B76" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C76" t="s">
         <v>32</v>
       </c>
       <c r="D76" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E76">
         <v>5</v>
@@ -14615,18 +14606,18 @@
         <v>5</v>
       </c>
       <c r="K76" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="77" spans="2:11">
       <c r="B77" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C77" t="s">
         <v>32</v>
       </c>
       <c r="D77" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E77">
         <v>5700</v>
@@ -14638,18 +14629,18 @@
         <v>5150</v>
       </c>
       <c r="K77" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="78" spans="2:11">
       <c r="B78" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C78" t="s">
         <v>32</v>
       </c>
       <c r="D78" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E78">
         <v>170</v>
@@ -14661,18 +14652,18 @@
         <v>155</v>
       </c>
       <c r="K78" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="79" spans="2:11">
       <c r="B79" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C79" t="s">
         <v>32</v>
       </c>
       <c r="D79" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E79">
         <v>4.306</v>
@@ -14684,18 +14675,18 @@
         <v>4.306</v>
       </c>
       <c r="K79" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="80" spans="2:11">
       <c r="B80" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C80" t="s">
         <v>32</v>
       </c>
       <c r="D80" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E80">
         <v>0.36</v>
@@ -14712,13 +14703,13 @@
     </row>
     <row r="81" spans="2:11">
       <c r="B81" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C81" t="s">
         <v>32</v>
       </c>
       <c r="D81" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E81">
         <v>40</v>
@@ -14739,18 +14730,18 @@
         <v>40</v>
       </c>
       <c r="K81" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="82" spans="2:11">
       <c r="B82" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="C82" t="s">
         <v>32</v>
       </c>
       <c r="D82" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E82">
         <v>5</v>
@@ -14771,12 +14762,12 @@
         <v>5</v>
       </c>
       <c r="K82" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="83" spans="2:11">
       <c r="B83" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C83" t="s">
         <v>36</v>
@@ -14794,12 +14785,12 @@
         <v>4500</v>
       </c>
       <c r="K83" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="84" spans="2:11">
       <c r="B84" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C84" t="s">
         <v>36</v>
@@ -14817,12 +14808,12 @@
         <v>160</v>
       </c>
       <c r="K84" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="85" spans="2:11">
       <c r="B85" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C85" t="s">
         <v>36</v>
@@ -14837,12 +14828,12 @@
         <v>0.77800000000000002</v>
       </c>
       <c r="K85" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="86" spans="2:11">
       <c r="B86" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C86" t="s">
         <v>36</v>
@@ -14869,12 +14860,12 @@
         <v>60</v>
       </c>
       <c r="K86" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="87" spans="2:11">
       <c r="B87" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C87" t="s">
         <v>36</v>
@@ -14901,12 +14892,12 @@
         <v>7</v>
       </c>
       <c r="K87" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="88" spans="2:11">
       <c r="B88" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C88" t="s">
         <v>36</v>
@@ -14930,12 +14921,12 @@
         <v>4884.6000000000004</v>
       </c>
       <c r="K88" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="89" spans="2:11">
       <c r="B89" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C89" t="s">
         <v>36</v>
@@ -14959,12 +14950,12 @@
         <v>136</v>
       </c>
       <c r="K89" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="90" spans="2:11">
       <c r="B90" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C90" t="s">
         <v>36</v>
@@ -14988,12 +14979,12 @@
         <v>0.72199999999999998</v>
       </c>
       <c r="K90" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="91" spans="2:11">
       <c r="B91" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C91" t="s">
         <v>36</v>
@@ -15020,12 +15011,12 @@
         <v>40</v>
       </c>
       <c r="K91" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="92" spans="2:11">
       <c r="B92" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="C92" t="s">
         <v>36</v>
@@ -15052,12 +15043,12 @@
         <v>3</v>
       </c>
       <c r="K92" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="93" spans="2:11">
       <c r="B93" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C93" t="s">
         <v>31</v>
@@ -15075,12 +15066,12 @@
         <v>2300</v>
       </c>
       <c r="K93" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="94" spans="2:11">
       <c r="B94" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C94" t="s">
         <v>31</v>
@@ -15098,12 +15089,12 @@
         <v>80</v>
       </c>
       <c r="K94" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="95" spans="2:11">
       <c r="B95" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C95" t="s">
         <v>31</v>
@@ -15121,12 +15112,12 @@
         <v>1.4570000000000001</v>
       </c>
       <c r="K95" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="96" spans="2:11">
       <c r="B96" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C96" t="s">
         <v>31</v>
@@ -15149,7 +15140,7 @@
     </row>
     <row r="97" spans="2:11">
       <c r="B97" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C97" t="s">
         <v>31</v>
@@ -15167,12 +15158,12 @@
         <v>0.6</v>
       </c>
       <c r="K97" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="98" spans="2:11">
       <c r="B98" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C98" t="s">
         <v>31</v>
@@ -15199,12 +15190,12 @@
         <v>45</v>
       </c>
       <c r="K98" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="99" spans="2:11">
       <c r="B99" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="C99" t="s">
         <v>31</v>
@@ -15231,12 +15222,12 @@
         <v>3</v>
       </c>
       <c r="K99" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="100" spans="2:11">
       <c r="B100" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C100" t="s">
         <v>31</v>
@@ -15254,12 +15245,12 @@
         <v>575</v>
       </c>
       <c r="K100" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="101" spans="2:11">
       <c r="B101" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C101" t="s">
         <v>31</v>
@@ -15277,12 +15268,12 @@
         <v>20</v>
       </c>
       <c r="K101" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="102" spans="2:11">
       <c r="B102" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C102" t="s">
         <v>31</v>
@@ -15300,12 +15291,12 @@
         <v>1.111</v>
       </c>
       <c r="K102" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="103" spans="2:11">
       <c r="B103" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C103" t="s">
         <v>31</v>
@@ -15328,7 +15319,7 @@
     </row>
     <row r="104" spans="2:11">
       <c r="B104" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C104" t="s">
         <v>31</v>
@@ -15346,12 +15337,12 @@
         <v>0.6</v>
       </c>
       <c r="K104" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="105" spans="2:11">
       <c r="B105" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C105" t="s">
         <v>31</v>
@@ -15378,12 +15369,12 @@
         <v>40</v>
       </c>
       <c r="K105" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="106" spans="2:11">
       <c r="B106" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="C106" t="s">
         <v>31</v>
@@ -15410,18 +15401,18 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="107" spans="2:11">
       <c r="B107" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C107" t="s">
         <v>31</v>
       </c>
       <c r="D107" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E107">
         <v>3750</v>
@@ -15433,18 +15424,18 @@
         <v>3550</v>
       </c>
       <c r="K107" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="108" spans="2:11">
       <c r="B108" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C108" t="s">
         <v>31</v>
       </c>
       <c r="D108" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E108">
         <v>140</v>
@@ -15456,18 +15447,18 @@
         <v>130</v>
       </c>
       <c r="K108" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="109" spans="2:11">
       <c r="B109" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C109" t="s">
         <v>31</v>
       </c>
       <c r="D109" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E109">
         <v>1.667</v>
@@ -15479,18 +15470,18 @@
         <v>1.667</v>
       </c>
       <c r="K109" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="110" spans="2:11">
       <c r="B110" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C110" t="s">
         <v>31</v>
       </c>
       <c r="D110" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E110">
         <v>0.38500000000000001</v>
@@ -15507,13 +15498,13 @@
     </row>
     <row r="111" spans="2:11">
       <c r="B111" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C111" t="s">
         <v>31</v>
       </c>
       <c r="D111" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E111">
         <v>0.7</v>
@@ -15525,18 +15516,18 @@
         <v>0.7</v>
       </c>
       <c r="K111" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="112" spans="2:11">
       <c r="B112" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C112" t="s">
         <v>31</v>
       </c>
       <c r="D112" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E112">
         <v>25</v>
@@ -15557,18 +15548,18 @@
         <v>25</v>
       </c>
       <c r="K112" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="113" spans="2:11">
       <c r="B113" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C113" t="s">
         <v>31</v>
       </c>
       <c r="D113" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E113">
         <v>2</v>
@@ -15589,18 +15580,18 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="114" spans="2:11">
       <c r="B114" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="C114" t="s">
         <v>31</v>
       </c>
       <c r="D114" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E114">
         <v>0.8</v>
@@ -15621,18 +15612,18 @@
         <v>0.8</v>
       </c>
       <c r="K114" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
     </row>
     <row r="115" spans="2:11">
       <c r="B115" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C115" t="s">
         <v>31</v>
       </c>
       <c r="D115" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E115">
         <v>5750</v>
@@ -15644,18 +15635,18 @@
         <v>5100</v>
       </c>
       <c r="K115" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="116" spans="2:11">
       <c r="B116" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C116" t="s">
         <v>31</v>
       </c>
       <c r="D116" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E116">
         <v>205</v>
@@ -15667,18 +15658,18 @@
         <v>180</v>
       </c>
       <c r="K116" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="117" spans="2:11">
       <c r="B117" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C117" t="s">
         <v>31</v>
       </c>
       <c r="D117" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E117">
         <v>2.3610000000000002</v>
@@ -15690,18 +15681,18 @@
         <v>2.3610000000000002</v>
       </c>
       <c r="K117" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="118" spans="2:11">
       <c r="B118" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C118" t="s">
         <v>31</v>
       </c>
       <c r="D118" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E118">
         <v>0.3</v>
@@ -15718,13 +15709,13 @@
     </row>
     <row r="119" spans="2:11">
       <c r="B119" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C119" t="s">
         <v>31</v>
       </c>
       <c r="D119" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E119">
         <v>0.6</v>
@@ -15736,18 +15727,18 @@
         <v>0.6</v>
       </c>
       <c r="K119" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="120" spans="2:11">
       <c r="B120" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C120" t="s">
         <v>31</v>
       </c>
       <c r="D120" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E120">
         <v>30</v>
@@ -15768,18 +15759,18 @@
         <v>30</v>
       </c>
       <c r="K120" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="121" spans="2:11">
       <c r="B121" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="C121" t="s">
         <v>31</v>
       </c>
       <c r="D121" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="E121">
         <v>3</v>
@@ -15800,12 +15791,12 @@
         <v>3</v>
       </c>
       <c r="K121" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="122" spans="2:11">
       <c r="B122" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C122" t="s">
         <v>34</v>
@@ -15823,12 +15814,12 @@
         <v>2550</v>
       </c>
       <c r="K122" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="123" spans="2:11">
       <c r="B123" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C123" t="s">
         <v>34</v>
@@ -15846,12 +15837,12 @@
         <v>50</v>
       </c>
       <c r="K123" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
     </row>
     <row r="124" spans="2:11">
       <c r="B124" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C124" t="s">
         <v>34</v>
@@ -15869,12 +15860,12 @@
         <v>0</v>
       </c>
       <c r="K124" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="125" spans="2:11">
       <c r="B125" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C125" t="s">
         <v>34</v>
@@ -15897,7 +15888,7 @@
     </row>
     <row r="126" spans="2:11">
       <c r="B126" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C126" t="s">
         <v>34</v>
@@ -15915,12 +15906,12 @@
         <v>0.85</v>
       </c>
       <c r="K126" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
     </row>
     <row r="127" spans="2:11">
       <c r="B127" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C127" t="s">
         <v>34</v>
@@ -15947,12 +15938,12 @@
         <v>30</v>
       </c>
       <c r="K127" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
     </row>
     <row r="128" spans="2:11">
       <c r="B128" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="C128" t="s">
         <v>34</v>
@@ -15979,7 +15970,7 @@
         <v>4</v>
       </c>
       <c r="K128" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
   </sheetData>
